--- a/docentes/De Jesús Orduña Sofía del Pilar - Estadisticos 20221.xlsx
+++ b/docentes/De Jesús Orduña Sofía del Pilar - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="27">
   <si>
     <t>Mat</t>
   </si>
@@ -71,6 +71,33 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>IXTLA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>ELIEL</t>
+  </si>
+  <si>
+    <t>ANGELA MONTSERRAT</t>
+  </si>
+  <si>
+    <t>JOSUE EDUARDO</t>
   </si>
 </sst>
 </file>
@@ -562,16 +589,19 @@
         <v>27</v>
       </c>
       <c r="D2">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>96.3</v>
+      </c>
+      <c r="H2">
+        <v>8.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -585,16 +615,19 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>85.70999999999999</v>
+      </c>
+      <c r="H3">
+        <v>7.3</v>
       </c>
     </row>
   </sheetData>
@@ -650,13 +683,13 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G2">
-        <v>100</v>
+        <v>96.3</v>
       </c>
       <c r="H2">
         <v>8.6</v>
@@ -676,16 +709,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G3">
-        <v>90.48</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H3">
-        <v>7.3</v>
+        <v>7.9</v>
       </c>
     </row>
   </sheetData>
@@ -695,7 +728,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -725,6 +758,75 @@
         <v>17</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>20330051920345</v>
+      </c>
+      <c r="B2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>20330051920383</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>21330051920334</v>
+      </c>
+      <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/De Jesús Orduña Sofía del Pilar - Estadisticos 20221.xlsx
+++ b/docentes/De Jesús Orduña Sofía del Pilar - Estadisticos 20221.xlsx
@@ -76,28 +76,28 @@
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
     <t>IXTLA</t>
   </si>
   <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
     <t>ELIEL</t>
   </si>
   <si>
+    <t>JOSUE EDUARDO</t>
+  </si>
+  <si>
     <t>ANGELA MONTSERRAT</t>
-  </si>
-  <si>
-    <t>JOSUE EDUARDO</t>
   </si>
 </sst>
 </file>
@@ -783,7 +783,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920383</v>
+        <v>21330051920334</v>
       </c>
       <c r="B3" t="s">
         <v>19</v>
@@ -795,18 +795,18 @@
         <v>25</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920334</v>
+        <v>20330051920383</v>
       </c>
       <c r="B4" t="s">
         <v>20</v>
@@ -818,10 +818,10 @@
         <v>26</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G4">
         <v>1</v>

--- a/docentes/De Jesús Orduña Sofía del Pilar - Estadisticos 20221.xlsx
+++ b/docentes/De Jesús Orduña Sofía del Pilar - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="18">
   <si>
     <t>Mat</t>
   </si>
@@ -71,33 +71,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>IXTLA</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>ELIEL</t>
-  </si>
-  <si>
-    <t>JOSUE EDUARDO</t>
-  </si>
-  <si>
-    <t>ANGELA MONTSERRAT</t>
   </si>
 </sst>
 </file>
@@ -683,16 +656,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G2">
-        <v>96.3</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -709,13 +682,13 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G3">
-        <v>85.70999999999999</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="H3">
         <v>7.9</v>
@@ -728,7 +701,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -758,75 +731,6 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>20330051920345</v>
-      </c>
-      <c r="B2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>21330051920334</v>
-      </c>
-      <c r="B3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>20330051920383</v>
-      </c>
-      <c r="B4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
